--- a/Team-Data/2011-12/2-20-2011-12.xlsx
+++ b/Team-Data/2011-12/2-20-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,58 +728,58 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E2" t="n">
         <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>0.594</v>
+        <v>0.613</v>
       </c>
       <c r="H2" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I2" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="J2" t="n">
-        <v>80.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L2" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M2" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.381</v>
+        <v>0.382</v>
       </c>
       <c r="O2" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="P2" t="n">
         <v>21</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.725</v>
+        <v>0.733</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S2" t="n">
         <v>31.3</v>
       </c>
       <c r="T2" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="U2" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="V2" t="n">
         <v>13.6</v>
@@ -721,7 +788,7 @@
         <v>8.1</v>
       </c>
       <c r="X2" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Y2" t="n">
         <v>4.9</v>
@@ -730,37 +797,37 @@
         <v>17.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>94</v>
+        <v>94.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>8</v>
       </c>
       <c r="AF2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL2" t="n">
         <v>6</v>
@@ -769,28 +836,28 @@
         <v>17</v>
       </c>
       <c r="AN2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AR2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS2" t="n">
         <v>12</v>
       </c>
       <c r="AT2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
         <v>3</v>
@@ -799,7 +866,7 @@
         <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -811,10 +878,10 @@
         <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -843,64 +910,64 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3" t="n">
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>0.484</v>
+        <v>0.5</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>34.1</v>
+        <v>34.3</v>
       </c>
       <c r="J3" t="n">
-        <v>75.2</v>
+        <v>75.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.454</v>
+        <v>0.456</v>
       </c>
       <c r="L3" t="n">
         <v>5.8</v>
       </c>
       <c r="M3" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="N3" t="n">
-        <v>0.38</v>
+        <v>0.384</v>
       </c>
       <c r="O3" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="P3" t="n">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
         <v>0.756</v>
       </c>
       <c r="R3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="S3" t="n">
-        <v>30.5</v>
+        <v>30.2</v>
       </c>
       <c r="T3" t="n">
-        <v>39</v>
+        <v>38.8</v>
       </c>
       <c r="U3" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V3" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W3" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X3" t="n">
         <v>5.7</v>
@@ -909,34 +976,34 @@
         <v>5.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>88.90000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
         <v>18</v>
       </c>
       <c r="AF3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH3" t="n">
         <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -951,10 +1018,10 @@
         <v>23</v>
       </c>
       <c r="AN3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP3" t="n">
         <v>27</v>
@@ -966,16 +1033,16 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
       </c>
       <c r="AU3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW3" t="n">
         <v>27</v>
@@ -984,19 +1051,19 @@
         <v>4</v>
       </c>
       <c r="AY3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA3" t="n">
         <v>19</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>21</v>
       </c>
       <c r="BB3" t="n">
         <v>26</v>
       </c>
       <c r="BC3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-14.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1115,13 +1182,13 @@
         <v>30</v>
       </c>
       <c r="AH4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI4" t="n">
         <v>28</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
         <v>29</v>
@@ -1133,19 +1200,19 @@
         <v>26</v>
       </c>
       <c r="AN4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP4" t="n">
         <v>23</v>
       </c>
       <c r="AQ4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR4" t="n">
         <v>25</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>24</v>
       </c>
       <c r="AS4" t="n">
         <v>22</v>
@@ -1166,7 +1233,7 @@
         <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ4" t="n">
         <v>11</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -1207,58 +1274,58 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" t="n">
         <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>0.765</v>
+        <v>0.758</v>
       </c>
       <c r="H5" t="n">
         <v>48</v>
       </c>
       <c r="I5" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.457</v>
+        <v>0.46</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.381</v>
+        <v>0.38</v>
       </c>
       <c r="O5" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P5" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q5" t="n">
         <v>0.728</v>
       </c>
       <c r="R5" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="S5" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T5" t="n">
-        <v>45.4</v>
+        <v>45.2</v>
       </c>
       <c r="U5" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="V5" t="n">
         <v>13.9</v>
@@ -1267,10 +1334,10 @@
         <v>7.4</v>
       </c>
       <c r="X5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z5" t="n">
         <v>17.7</v>
@@ -1279,10 +1346,10 @@
         <v>18</v>
       </c>
       <c r="AB5" t="n">
-        <v>97</v>
+        <v>97.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
@@ -1297,16 +1364,16 @@
         <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI5" t="n">
         <v>7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL5" t="n">
         <v>18</v>
@@ -1315,16 +1382,16 @@
         <v>20</v>
       </c>
       <c r="AN5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AR5" t="n">
         <v>2</v>
@@ -1345,22 +1412,22 @@
         <v>21</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="n">
         <v>3</v>
       </c>
       <c r="BA5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB5" t="n">
         <v>9</v>
       </c>
       <c r="BC5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -1467,31 +1534,31 @@
         <v>-3.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE6" t="n">
         <v>22</v>
       </c>
       <c r="AF6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG6" t="n">
         <v>21</v>
       </c>
       <c r="AH6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI6" t="n">
         <v>21</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK6" t="n">
         <v>25</v>
       </c>
       <c r="AL6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AM6" t="n">
         <v>16</v>
@@ -1512,10 +1579,10 @@
         <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
         <v>18</v>
@@ -1536,7 +1603,7 @@
         <v>23</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
         <v>19</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
         <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>0.636</v>
+        <v>0.625</v>
       </c>
       <c r="H7" t="n">
         <v>48.5</v>
@@ -1589,43 +1656,43 @@
         <v>35.8</v>
       </c>
       <c r="J7" t="n">
-        <v>81.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L7" t="n">
         <v>7.1</v>
       </c>
       <c r="M7" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.329</v>
+        <v>0.33</v>
       </c>
       <c r="O7" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="P7" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.742</v>
+        <v>0.743</v>
       </c>
       <c r="R7" t="n">
         <v>10.4</v>
       </c>
       <c r="S7" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="T7" t="n">
-        <v>43.5</v>
+        <v>43.3</v>
       </c>
       <c r="U7" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V7" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W7" t="n">
         <v>9.1</v>
@@ -1634,22 +1701,22 @@
         <v>5.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
         <v>18.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>94.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
         <v>5</v>
@@ -1658,16 +1725,16 @@
         <v>6</v>
       </c>
       <c r="AG7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI7" t="n">
         <v>16</v>
       </c>
       <c r="AJ7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK7" t="n">
         <v>17</v>
@@ -1679,7 +1746,7 @@
         <v>5</v>
       </c>
       <c r="AN7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO7" t="n">
         <v>20</v>
@@ -1688,19 +1755,19 @@
         <v>19</v>
       </c>
       <c r="AQ7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AR7" t="n">
         <v>22</v>
       </c>
       <c r="AS7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
         <v>9</v>
@@ -1709,7 +1776,7 @@
         <v>3</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY7" t="n">
         <v>6</v>
@@ -1721,7 +1788,7 @@
         <v>22</v>
       </c>
       <c r="BB7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC7" t="n">
         <v>7</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -1753,55 +1820,55 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" t="n">
         <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>0.545</v>
+        <v>0.531</v>
       </c>
       <c r="H8" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="I8" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J8" t="n">
-        <v>81</v>
+        <v>80.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0.472</v>
+        <v>0.474</v>
       </c>
       <c r="L8" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M8" t="n">
         <v>20.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0.324</v>
+        <v>0.327</v>
       </c>
       <c r="O8" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="P8" t="n">
-        <v>28.2</v>
+        <v>27.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.733</v>
+        <v>0.735</v>
       </c>
       <c r="R8" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="S8" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="T8" t="n">
-        <v>43.1</v>
+        <v>42.6</v>
       </c>
       <c r="U8" t="n">
         <v>22.8</v>
@@ -1813,13 +1880,13 @@
         <v>9</v>
       </c>
       <c r="X8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y8" t="n">
         <v>6.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AA8" t="n">
         <v>23.3</v>
@@ -1831,16 +1898,16 @@
         <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH8" t="n">
         <v>2</v>
@@ -1849,19 +1916,19 @@
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK8" t="n">
         <v>3</v>
       </c>
       <c r="AL8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM8" t="n">
         <v>7</v>
       </c>
       <c r="AN8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO8" t="n">
         <v>3</v>
@@ -1873,13 +1940,13 @@
         <v>21</v>
       </c>
       <c r="AR8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AU8" t="n">
         <v>2</v>
@@ -1891,7 +1958,7 @@
         <v>4</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AY8" t="n">
         <v>30</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -2013,10 +2080,10 @@
         <v>-6.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF9" t="n">
         <v>25</v>
@@ -2025,7 +2092,7 @@
         <v>24</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
         <v>26</v>
@@ -2040,7 +2107,7 @@
         <v>26</v>
       </c>
       <c r="AM9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN9" t="n">
         <v>16</v>
@@ -2049,7 +2116,7 @@
         <v>14</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ9" t="n">
         <v>10</v>
@@ -2088,7 +2155,7 @@
         <v>27</v>
       </c>
       <c r="BC9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -2117,25 +2184,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
         <v>17</v>
       </c>
       <c r="G10" t="n">
-        <v>0.414</v>
+        <v>0.393</v>
       </c>
       <c r="H10" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I10" t="n">
         <v>37.6</v>
       </c>
       <c r="J10" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K10" t="n">
         <v>0.459</v>
@@ -2144,25 +2211,25 @@
         <v>8.300000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="N10" t="n">
-        <v>0.394</v>
+        <v>0.395</v>
       </c>
       <c r="O10" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P10" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.746</v>
+        <v>0.744</v>
       </c>
       <c r="R10" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S10" t="n">
-        <v>28.9</v>
+        <v>29.1</v>
       </c>
       <c r="T10" t="n">
         <v>39.6</v>
@@ -2171,40 +2238,40 @@
         <v>22.6</v>
       </c>
       <c r="V10" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="W10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X10" t="n">
         <v>5.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="AA10" t="n">
         <v>18</v>
       </c>
       <c r="AB10" t="n">
-        <v>99</v>
+        <v>98.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.6</v>
+        <v>-1.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
         <v>12</v>
@@ -2216,7 +2283,7 @@
         <v>9</v>
       </c>
       <c r="AK10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
@@ -2228,10 +2295,10 @@
         <v>2</v>
       </c>
       <c r="AO10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ10" t="n">
         <v>15</v>
@@ -2249,7 +2316,7 @@
         <v>3</v>
       </c>
       <c r="AV10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2264,13 +2331,13 @@
         <v>29</v>
       </c>
       <c r="BA10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB10" t="n">
         <v>4</v>
       </c>
       <c r="BC10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -2299,25 +2366,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F11" t="n">
         <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>0.576</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>48.5</v>
       </c>
       <c r="I11" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J11" t="n">
-        <v>83.8</v>
+        <v>84.2</v>
       </c>
       <c r="K11" t="n">
         <v>0.451</v>
@@ -2326,28 +2393,28 @@
         <v>7.1</v>
       </c>
       <c r="M11" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O11" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="P11" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="R11" t="n">
         <v>11.9</v>
       </c>
       <c r="S11" t="n">
-        <v>30.7</v>
+        <v>30.9</v>
       </c>
       <c r="T11" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="U11" t="n">
         <v>20.8</v>
@@ -2359,28 +2426,28 @@
         <v>7.9</v>
       </c>
       <c r="X11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="n">
         <v>5.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="AB11" t="n">
         <v>97.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AF11" t="n">
         <v>12</v>
@@ -2389,7 +2456,7 @@
         <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI11" t="n">
         <v>3</v>
@@ -2407,25 +2474,25 @@
         <v>11</v>
       </c>
       <c r="AN11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO11" t="n">
         <v>28</v>
       </c>
       <c r="AP11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ11" t="n">
         <v>3</v>
       </c>
       <c r="AR11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT11" t="n">
         <v>12</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>14</v>
       </c>
       <c r="AU11" t="n">
         <v>15</v>
@@ -2443,7 +2510,7 @@
         <v>19</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
         <v>29</v>
@@ -2452,7 +2519,7 @@
         <v>7</v>
       </c>
       <c r="BC11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
         <v>8</v>
@@ -2571,7 +2638,7 @@
         <v>9</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
         <v>22</v>
@@ -2622,19 +2689,19 @@
         <v>8</v>
       </c>
       <c r="AY12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
         <v>26</v>
       </c>
       <c r="BA12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -2663,82 +2730,82 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" t="n">
         <v>19</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>0.633</v>
+        <v>0.655</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>36.4</v>
+        <v>36.6</v>
       </c>
       <c r="J13" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M13" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.356</v>
+        <v>0.353</v>
       </c>
       <c r="O13" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P13" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S13" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T13" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U13" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="V13" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="W13" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.7</v>
+        <v>97.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD13" t="n">
         <v>28</v>
@@ -2750,7 +2817,7 @@
         <v>5</v>
       </c>
       <c r="AG13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH13" t="n">
         <v>6</v>
@@ -2762,7 +2829,7 @@
         <v>19</v>
       </c>
       <c r="AK13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL13" t="n">
         <v>5</v>
@@ -2777,37 +2844,37 @@
         <v>12</v>
       </c>
       <c r="AP13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ13" t="n">
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU13" t="n">
         <v>11</v>
       </c>
       <c r="AV13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AY13" t="n">
         <v>4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA13" t="n">
         <v>4</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -2845,70 +2912,70 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F14" t="n">
         <v>13</v>
       </c>
       <c r="G14" t="n">
-        <v>0.594</v>
+        <v>0.581</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J14" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K14" t="n">
         <v>0.45</v>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M14" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="O14" t="n">
         <v>16.7</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.301</v>
-      </c>
-      <c r="O14" t="n">
-        <v>16.8</v>
       </c>
       <c r="P14" t="n">
         <v>22.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.744</v>
+        <v>0.74</v>
       </c>
       <c r="R14" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S14" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="T14" t="n">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="U14" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V14" t="n">
         <v>15.1</v>
       </c>
       <c r="W14" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="X14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z14" t="n">
         <v>18.5</v>
@@ -2917,22 +2984,22 @@
         <v>19.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>93.3</v>
+        <v>93</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AF14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH14" t="n">
         <v>14</v>
@@ -2953,7 +3020,7 @@
         <v>19</v>
       </c>
       <c r="AN14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO14" t="n">
         <v>15</v>
@@ -2962,10 +3029,10 @@
         <v>13</v>
       </c>
       <c r="AQ14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2974,7 +3041,7 @@
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV14" t="n">
         <v>16</v>
@@ -2983,7 +3050,7 @@
         <v>29</v>
       </c>
       <c r="AX14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -2995,10 +3062,10 @@
         <v>15</v>
       </c>
       <c r="BB14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" t="n">
         <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G15" t="n">
-        <v>0.545</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H15" t="n">
         <v>48.2</v>
@@ -3045,25 +3112,25 @@
         <v>36.4</v>
       </c>
       <c r="J15" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K15" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L15" t="n">
         <v>3.6</v>
       </c>
       <c r="M15" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.32</v>
+        <v>0.323</v>
       </c>
       <c r="O15" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P15" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q15" t="n">
         <v>0.755</v>
@@ -3072,28 +3139,28 @@
         <v>12.4</v>
       </c>
       <c r="S15" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T15" t="n">
-        <v>42.1</v>
+        <v>42.3</v>
       </c>
       <c r="U15" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="V15" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W15" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="X15" t="n">
         <v>5.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="AA15" t="n">
         <v>20</v>
@@ -3102,19 +3169,19 @@
         <v>93.59999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AF15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
         <v>25</v>
@@ -3123,10 +3190,10 @@
         <v>12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL15" t="n">
         <v>30</v>
@@ -3135,7 +3202,7 @@
         <v>30</v>
       </c>
       <c r="AN15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO15" t="n">
         <v>11</v>
@@ -3150,7 +3217,7 @@
         <v>5</v>
       </c>
       <c r="AS15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT15" t="n">
         <v>16</v>
@@ -3159,16 +3226,16 @@
         <v>25</v>
       </c>
       <c r="AV15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
       </c>
       <c r="AX15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AZ15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -3287,10 +3354,10 @@
         <v>9.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
         <v>1</v>
@@ -3299,7 +3366,7 @@
         <v>1</v>
       </c>
       <c r="AH16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
         <v>1</v>
@@ -3314,7 +3381,7 @@
         <v>19</v>
       </c>
       <c r="AM16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN16" t="n">
         <v>1</v>
@@ -3326,22 +3393,22 @@
         <v>3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR16" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AS16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW16" t="n">
         <v>8</v>
@@ -3353,7 +3420,7 @@
         <v>3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA16" t="n">
         <v>5</v>
@@ -3362,7 +3429,7 @@
         <v>2</v>
       </c>
       <c r="BC16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" t="n">
         <v>13</v>
       </c>
       <c r="F17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G17" t="n">
-        <v>0.406</v>
+        <v>0.419</v>
       </c>
       <c r="H17" t="n">
         <v>48.2</v>
@@ -3409,43 +3476,43 @@
         <v>35.8</v>
       </c>
       <c r="J17" t="n">
-        <v>84.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0.424</v>
       </c>
       <c r="L17" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M17" t="n">
         <v>20.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.333</v>
+        <v>0.337</v>
       </c>
       <c r="O17" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P17" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.792</v>
+        <v>0.791</v>
       </c>
       <c r="R17" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="T17" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U17" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V17" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W17" t="n">
         <v>7.9</v>
@@ -3454,37 +3521,37 @@
         <v>5.2</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z17" t="n">
         <v>20</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>94.7</v>
+        <v>94.8</v>
       </c>
       <c r="AC17" t="n">
         <v>-1.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF17" t="n">
         <v>22</v>
       </c>
       <c r="AG17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AH17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ17" t="n">
         <v>1</v>
@@ -3493,7 +3560,7 @@
         <v>27</v>
       </c>
       <c r="AL17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM17" t="n">
         <v>8</v>
@@ -3502,10 +3569,10 @@
         <v>17</v>
       </c>
       <c r="AO17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP17" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AQ17" t="n">
         <v>2</v>
@@ -3532,7 +3599,7 @@
         <v>12</v>
       </c>
       <c r="AY17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ17" t="n">
         <v>15</v>
@@ -3544,7 +3611,7 @@
         <v>14</v>
       </c>
       <c r="BC17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -3573,37 +3640,37 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" t="n">
         <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>0.485</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
-        <v>48.2</v>
+        <v>48</v>
       </c>
       <c r="I18" t="n">
         <v>35.1</v>
       </c>
       <c r="J18" t="n">
-        <v>81.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.431</v>
+        <v>0.433</v>
       </c>
       <c r="L18" t="n">
         <v>6.3</v>
       </c>
       <c r="M18" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.316</v>
+        <v>0.32</v>
       </c>
       <c r="O18" t="n">
         <v>20.2</v>
@@ -3612,19 +3679,19 @@
         <v>26</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.779</v>
+        <v>0.774</v>
       </c>
       <c r="R18" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S18" t="n">
         <v>32.7</v>
       </c>
       <c r="T18" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
       <c r="U18" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="V18" t="n">
         <v>16.2</v>
@@ -3633,25 +3700,25 @@
         <v>7.7</v>
       </c>
       <c r="X18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="AA18" t="n">
         <v>22.3</v>
       </c>
       <c r="AB18" t="n">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3663,22 +3730,22 @@
         <v>16</v>
       </c>
       <c r="AH18" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI18" t="n">
         <v>19</v>
       </c>
       <c r="AJ18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AK18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN18" t="n">
         <v>23</v>
@@ -3693,7 +3760,7 @@
         <v>7</v>
       </c>
       <c r="AR18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AS18" t="n">
         <v>6</v>
@@ -3702,7 +3769,7 @@
         <v>3</v>
       </c>
       <c r="AU18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV18" t="n">
         <v>27</v>
@@ -3711,10 +3778,10 @@
         <v>19</v>
       </c>
       <c r="AX18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ18" t="n">
         <v>7</v>
@@ -3726,7 +3793,7 @@
         <v>10</v>
       </c>
       <c r="BC18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -3755,61 +3822,61 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
         <v>24</v>
       </c>
       <c r="G19" t="n">
-        <v>0.294</v>
+        <v>0.273</v>
       </c>
       <c r="H19" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="I19" t="n">
         <v>33.4</v>
       </c>
       <c r="J19" t="n">
-        <v>79.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.421</v>
+        <v>0.422</v>
       </c>
       <c r="L19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="M19" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0.356</v>
+        <v>0.351</v>
       </c>
       <c r="O19" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P19" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.772</v>
+        <v>0.774</v>
       </c>
       <c r="R19" t="n">
         <v>12.3</v>
       </c>
       <c r="S19" t="n">
-        <v>27.2</v>
+        <v>27</v>
       </c>
       <c r="T19" t="n">
-        <v>39.5</v>
+        <v>39.3</v>
       </c>
       <c r="U19" t="n">
         <v>19.9</v>
       </c>
       <c r="V19" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W19" t="n">
         <v>6.9</v>
@@ -3821,31 +3888,31 @@
         <v>5.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>92.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>-6.4</v>
+        <v>-6.9</v>
       </c>
       <c r="AD19" t="n">
         <v>1</v>
       </c>
       <c r="AE19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG19" t="n">
         <v>27</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AH19" t="n">
         <v>26</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>28</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3863,13 +3930,13 @@
         <v>2</v>
       </c>
       <c r="AN19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO19" t="n">
         <v>13</v>
       </c>
       <c r="AP19" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AQ19" t="n">
         <v>9</v>
@@ -3887,28 +3954,28 @@
         <v>20</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW19" t="n">
         <v>26</v>
       </c>
       <c r="AX19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY19" t="n">
         <v>20</v>
       </c>
       <c r="AZ19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB19" t="n">
         <v>24</v>
       </c>
       <c r="BC19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E20" t="n">
         <v>7</v>
       </c>
       <c r="F20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20" t="n">
-        <v>0.226</v>
+        <v>0.233</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
@@ -3955,40 +4022,40 @@
         <v>34.2</v>
       </c>
       <c r="J20" t="n">
-        <v>78.2</v>
+        <v>77.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.437</v>
+        <v>0.44</v>
       </c>
       <c r="L20" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="M20" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.316</v>
+        <v>0.309</v>
       </c>
       <c r="O20" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="P20" t="n">
         <v>20.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.744</v>
+        <v>0.739</v>
       </c>
       <c r="R20" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S20" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T20" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="U20" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V20" t="n">
         <v>15.5</v>
@@ -4000,28 +4067,28 @@
         <v>4.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA20" t="n">
         <v>18.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>87.5</v>
+        <v>87.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>-5.3</v>
+        <v>-5.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
       </c>
       <c r="AF20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG20" t="n">
         <v>28</v>
@@ -4030,16 +4097,16 @@
         <v>18</v>
       </c>
       <c r="AI20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK20" t="n">
         <v>18</v>
       </c>
       <c r="AL20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM20" t="n">
         <v>29</v>
@@ -4048,13 +4115,13 @@
         <v>24</v>
       </c>
       <c r="AO20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ20" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AR20" t="n">
         <v>15</v>
@@ -4063,7 +4130,7 @@
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU20" t="n">
         <v>21</v>
@@ -4072,13 +4139,13 @@
         <v>22</v>
       </c>
       <c r="AW20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX20" t="n">
         <v>21</v>
       </c>
       <c r="AY20" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AZ20" t="n">
         <v>21</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -4119,37 +4186,37 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21" t="n">
         <v>16</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>0.485</v>
+        <v>0.5</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="J21" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K21" t="n">
-        <v>0.432</v>
+        <v>0.433</v>
       </c>
       <c r="L21" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M21" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.301</v>
+        <v>0.303</v>
       </c>
       <c r="O21" t="n">
         <v>19</v>
@@ -4158,7 +4225,7 @@
         <v>25.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R21" t="n">
         <v>10.8</v>
@@ -4170,7 +4237,7 @@
         <v>41.6</v>
       </c>
       <c r="U21" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="V21" t="n">
         <v>16.8</v>
@@ -4179,25 +4246,25 @@
         <v>9.4</v>
       </c>
       <c r="X21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AA21" t="n">
         <v>22.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE21" t="n">
         <v>16</v>
@@ -4209,25 +4276,25 @@
         <v>16</v>
       </c>
       <c r="AH21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
         <v>20</v>
       </c>
       <c r="AJ21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AM21" t="n">
         <v>3</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO21" t="n">
         <v>6</v>
@@ -4242,10 +4309,10 @@
         <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU21" t="n">
         <v>23</v>
@@ -4257,13 +4324,13 @@
         <v>2</v>
       </c>
       <c r="AX21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY21" t="n">
         <v>15</v>
       </c>
       <c r="AZ21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA21" t="n">
         <v>2</v>
@@ -4272,7 +4339,7 @@
         <v>12</v>
       </c>
       <c r="BC21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F22" t="n">
         <v>7</v>
       </c>
       <c r="G22" t="n">
-        <v>0.781</v>
+        <v>0.774</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4319,76 +4386,76 @@
         <v>37</v>
       </c>
       <c r="J22" t="n">
-        <v>77.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="K22" t="n">
         <v>0.475</v>
       </c>
       <c r="L22" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M22" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
       <c r="O22" t="n">
         <v>21.6</v>
       </c>
       <c r="P22" t="n">
-        <v>27.1</v>
+        <v>27.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.797</v>
+        <v>0.795</v>
       </c>
       <c r="R22" t="n">
         <v>10.5</v>
       </c>
       <c r="S22" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="T22" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U22" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="V22" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="W22" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="X22" t="n">
         <v>7.8</v>
       </c>
-      <c r="X22" t="n">
-        <v>8</v>
-      </c>
       <c r="Y22" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z22" t="n">
         <v>20.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB22" t="n">
         <v>102.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF22" t="n">
         <v>1</v>
       </c>
       <c r="AG22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
         <v>14</v>
@@ -4397,13 +4464,13 @@
         <v>8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK22" t="n">
         <v>2</v>
       </c>
       <c r="AL22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM22" t="n">
         <v>15</v>
@@ -4424,7 +4491,7 @@
         <v>21</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
         <v>6</v>
@@ -4436,19 +4503,19 @@
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ22" t="n">
         <v>22</v>
       </c>
       <c r="BA22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F23" t="n">
         <v>12</v>
       </c>
       <c r="G23" t="n">
-        <v>0.636</v>
+        <v>0.625</v>
       </c>
       <c r="H23" t="n">
         <v>48.5</v>
@@ -4501,40 +4568,40 @@
         <v>33.4</v>
       </c>
       <c r="J23" t="n">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="K23" t="n">
         <v>0.434</v>
       </c>
       <c r="L23" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="M23" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="N23" t="n">
-        <v>0.39</v>
+        <v>0.391</v>
       </c>
       <c r="O23" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P23" t="n">
         <v>24.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.656</v>
+        <v>0.653</v>
       </c>
       <c r="R23" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="S23" t="n">
         <v>32.6</v>
       </c>
       <c r="T23" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U23" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V23" t="n">
         <v>15.1</v>
@@ -4543,7 +4610,7 @@
         <v>6.3</v>
       </c>
       <c r="X23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y23" t="n">
         <v>4.5</v>
@@ -4552,7 +4619,7 @@
         <v>18</v>
       </c>
       <c r="AA23" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB23" t="n">
         <v>93.09999999999999</v>
@@ -4561,7 +4628,7 @@
         <v>2</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE23" t="n">
         <v>5</v>
@@ -4570,10 +4637,10 @@
         <v>6</v>
       </c>
       <c r="AG23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI23" t="n">
         <v>29</v>
@@ -4591,10 +4658,10 @@
         <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP23" t="n">
         <v>11</v>
@@ -4603,10 +4670,10 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT23" t="n">
         <v>9</v>
@@ -4621,7 +4688,7 @@
         <v>28</v>
       </c>
       <c r="AX23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY23" t="n">
         <v>8</v>
@@ -4630,13 +4697,13 @@
         <v>5</v>
       </c>
       <c r="BA23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -4743,19 +4810,19 @@
         <v>7.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF24" t="n">
         <v>6</v>
       </c>
       <c r="AG24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AH24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI24" t="n">
         <v>5</v>
@@ -4764,7 +4831,7 @@
         <v>5</v>
       </c>
       <c r="AK24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL24" t="n">
         <v>20</v>
@@ -4779,10 +4846,10 @@
         <v>30</v>
       </c>
       <c r="AP24" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR24" t="n">
         <v>29</v>
@@ -4791,10 +4858,10 @@
         <v>2</v>
       </c>
       <c r="AT24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV24" t="n">
         <v>1</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F25" t="n">
         <v>19</v>
       </c>
       <c r="G25" t="n">
-        <v>0.424</v>
+        <v>0.406</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
@@ -4865,7 +4932,7 @@
         <v>36.2</v>
       </c>
       <c r="J25" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K25" t="n">
         <v>0.446</v>
@@ -4880,25 +4947,25 @@
         <v>0.344</v>
       </c>
       <c r="O25" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="P25" t="n">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.775</v>
+        <v>0.774</v>
       </c>
       <c r="R25" t="n">
         <v>9.9</v>
       </c>
       <c r="S25" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="T25" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U25" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V25" t="n">
         <v>14.8</v>
@@ -4910,40 +4977,40 @@
         <v>5.3</v>
       </c>
       <c r="Y25" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="AA25" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>94.3</v>
+        <v>94</v>
       </c>
       <c r="AC25" t="n">
-        <v>-2.5</v>
+        <v>-3.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>20</v>
       </c>
       <c r="AF25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG25" t="n">
         <v>22</v>
       </c>
-      <c r="AG25" t="n">
-        <v>20</v>
-      </c>
       <c r="AH25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI25" t="n">
         <v>13</v>
       </c>
       <c r="AJ25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AK25" t="n">
         <v>13</v>
@@ -4958,7 +5025,7 @@
         <v>15</v>
       </c>
       <c r="AO25" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP25" t="n">
         <v>28</v>
@@ -4967,10 +5034,10 @@
         <v>8</v>
       </c>
       <c r="AR25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT25" t="n">
         <v>25</v>
@@ -4979,13 +5046,13 @@
         <v>5</v>
       </c>
       <c r="AV25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW25" t="n">
         <v>22</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
@@ -4994,10 +5061,10 @@
         <v>8</v>
       </c>
       <c r="BA25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC25" t="n">
         <v>22</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -5029,37 +5096,37 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E26" t="n">
         <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G26" t="n">
-        <v>0.515</v>
+        <v>0.531</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="J26" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K26" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L26" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.329</v>
+        <v>0.322</v>
       </c>
       <c r="O26" t="n">
         <v>17.6</v>
@@ -5068,61 +5135,61 @@
         <v>22.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.782</v>
+        <v>0.783</v>
       </c>
       <c r="R26" t="n">
         <v>11.2</v>
       </c>
       <c r="S26" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T26" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="U26" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V26" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W26" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X26" t="n">
         <v>5.2</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z26" t="n">
         <v>20</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH26" t="n">
         <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ26" t="n">
         <v>6</v>
@@ -5131,13 +5198,13 @@
         <v>16</v>
       </c>
       <c r="AL26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM26" t="n">
         <v>14</v>
       </c>
       <c r="AN26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AO26" t="n">
         <v>9</v>
@@ -5146,13 +5213,13 @@
         <v>14</v>
       </c>
       <c r="AQ26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR26" t="n">
         <v>16</v>
       </c>
       <c r="AS26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT26" t="n">
         <v>17</v>
@@ -5164,25 +5231,25 @@
         <v>7</v>
       </c>
       <c r="AW26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ26" t="n">
         <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB26" t="n">
         <v>8</v>
       </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5301,7 +5368,7 @@
         <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI27" t="n">
         <v>23</v>
@@ -5316,7 +5383,7 @@
         <v>17</v>
       </c>
       <c r="AM27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN27" t="n">
         <v>25</v>
@@ -5325,16 +5392,16 @@
         <v>8</v>
       </c>
       <c r="AP27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AR27" t="n">
         <v>1</v>
       </c>
       <c r="AS27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT27" t="n">
         <v>4</v>
@@ -5343,7 +5410,7 @@
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW27" t="n">
         <v>11</v>
@@ -5361,7 +5428,7 @@
         <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -5393,55 +5460,55 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F28" t="n">
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0.719</v>
+        <v>0.71</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
       </c>
       <c r="I28" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J28" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K28" t="n">
         <v>0.461</v>
       </c>
       <c r="L28" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M28" t="n">
         <v>20</v>
       </c>
       <c r="N28" t="n">
-        <v>0.39</v>
+        <v>0.387</v>
       </c>
       <c r="O28" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="P28" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.726</v>
+        <v>0.723</v>
       </c>
       <c r="R28" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S28" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="T28" t="n">
-        <v>41.4</v>
+        <v>41.7</v>
       </c>
       <c r="U28" t="n">
         <v>22.4</v>
@@ -5450,7 +5517,7 @@
         <v>13.5</v>
       </c>
       <c r="W28" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X28" t="n">
         <v>4.5</v>
@@ -5462,16 +5529,16 @@
         <v>17.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>98.90000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="AC28" t="n">
         <v>4.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -5501,16 +5568,16 @@
         <v>10</v>
       </c>
       <c r="AN28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AP28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR28" t="n">
         <v>26</v>
@@ -5519,7 +5586,7 @@
         <v>10</v>
       </c>
       <c r="AT28" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AU28" t="n">
         <v>4</v>
@@ -5540,13 +5607,13 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB28" t="n">
         <v>5</v>
       </c>
       <c r="BC28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>-5.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF29" t="n">
         <v>26</v>
       </c>
       <c r="AG29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH29" t="n">
         <v>8</v>
@@ -5689,25 +5756,25 @@
         <v>21</v>
       </c>
       <c r="AP29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ29" t="n">
         <v>14</v>
       </c>
       <c r="AR29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW29" t="n">
         <v>23</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -5757,61 +5824,61 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E30" t="n">
         <v>15</v>
       </c>
       <c r="F30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G30" t="n">
-        <v>0.484</v>
+        <v>0.5</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J30" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L30" t="n">
         <v>3.8</v>
       </c>
       <c r="M30" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="N30" t="n">
-        <v>0.299</v>
+        <v>0.298</v>
       </c>
       <c r="O30" t="n">
         <v>18.8</v>
       </c>
       <c r="P30" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.746</v>
+        <v>0.743</v>
       </c>
       <c r="R30" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S30" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T30" t="n">
         <v>42.4</v>
       </c>
       <c r="U30" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V30" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W30" t="n">
         <v>7.9</v>
@@ -5826,43 +5893,43 @@
         <v>22.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>96.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE30" t="n">
         <v>18</v>
       </c>
       <c r="AF30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH30" t="n">
         <v>7</v>
       </c>
       <c r="AI30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK30" t="n">
         <v>11</v>
       </c>
       <c r="AL30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN30" t="n">
         <v>29</v>
@@ -5877,7 +5944,7 @@
         <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS30" t="n">
         <v>21</v>
@@ -5886,10 +5953,10 @@
         <v>15</v>
       </c>
       <c r="AU30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW30" t="n">
         <v>15</v>
@@ -5898,13 +5965,13 @@
         <v>3</v>
       </c>
       <c r="AY30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ30" t="n">
         <v>28</v>
       </c>
       <c r="BA30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB30" t="n">
         <v>11</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31" t="n">
         <v>7</v>
       </c>
       <c r="F31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G31" t="n">
-        <v>0.219</v>
+        <v>0.226</v>
       </c>
       <c r="H31" t="n">
         <v>48.2</v>
@@ -5966,40 +6033,40 @@
         <v>4.4</v>
       </c>
       <c r="M31" t="n">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0.299</v>
+        <v>0.301</v>
       </c>
       <c r="O31" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="P31" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.726</v>
+        <v>0.731</v>
       </c>
       <c r="R31" t="n">
         <v>11.8</v>
       </c>
       <c r="S31" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="T31" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U31" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="V31" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="W31" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X31" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="Y31" t="n">
         <v>4.9</v>
@@ -6011,25 +6078,25 @@
         <v>18.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>91.40000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>-9</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
       </c>
       <c r="AF31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI31" t="n">
         <v>18</v>
@@ -6044,28 +6111,28 @@
         <v>25</v>
       </c>
       <c r="AM31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN31" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AQ31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS31" t="n">
         <v>26</v>
       </c>
       <c r="AT31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU31" t="n">
         <v>29</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-20-2011-12</t>
+          <t>2012-02-20</t>
         </is>
       </c>
     </row>
